--- a/Report_5_4_L4-E2ETests_VietTien_v1_3.xlsx
+++ b/Report_5_4_L4-E2ETests_VietTien_v1_3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\files2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEP_Deploy\SEP490_be\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFB29B9-DF4D-4319-8B31-E343E0B80066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1A936A-9F3C-4F63-9575-4F2C7C2B5CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="20970" windowHeight="15585" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="0" windowWidth="20970" windowHeight="15585" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="444">
   <si>
     <t>Level 4 — E2E Test  |  Test Case Specification Template</t>
   </si>
@@ -711,6 +708,12 @@
 Biên bản bàn giao lưu đủ 2 danh tính + thời điểm</t>
   </si>
   <si>
+    <t>DEF-L4-001</t>
+  </si>
+  <si>
+    <t>sales-confirm tra 403 cho tai khoan SalesStaff. HandoverController.cs:35-36 khai role "Sales" — gia tri khong ton tai trong enum SystemRole -&gt; khong the du 2 chu ky.</t>
+  </si>
+  <si>
     <t>FT-07</t>
   </si>
   <si>
@@ -732,6 +735,12 @@
     <t>Đơn chuyển 'Đang giao'
 Không cho lưu khi thiếu ảnh hoặc chữ ký
 Sau khi đủ bằng chứng: trạng thái 'Đã giao'</t>
+  </si>
+  <si>
+    <t>DEF-L4-002</t>
+  </si>
+  <si>
+    <t>GET /api/delivery/trips -&gt; 404. Module chuyen giao hang chua trien khai (trung DEF-L3-004).</t>
   </si>
   <si>
     <t>FT-01</t>
@@ -945,6 +954,9 @@
 Đơn B: hiển thị cảnh báo 'ĐÃ THANH TOÁN — KHÔNG THU TIỀN', ô nhập bị khoá</t>
   </si>
   <si>
+    <t>GET /api/delivery/collections -&gt; 404. Thu COD chua co endpoint (trung DEF-L3-004).</t>
+  </si>
+  <si>
     <t>FT-08</t>
   </si>
   <si>
@@ -1055,6 +1067,12 @@
 Sau post: tồn đổi đúng phần chênh lệch</t>
   </si>
   <si>
+    <t>DEF-L4-003</t>
+  </si>
+  <si>
+    <t>GET /api/inventory/count-sessions -&gt; 404. Phien kiem ke chua trien khai (trung DEF-L3-005).</t>
+  </si>
+  <si>
     <t>/warehouse/production/issue</t>
   </si>
   <si>
@@ -1086,6 +1104,9 @@
 Xuống thêm không sinh cảnh báo thứ hai mà cập nhật cảnh báo đang có</t>
   </si>
   <si>
+    <t>GET /api/inventory/low-stock-alerts -&gt; 404. Canh bao ton thap chua co endpoint (trung DEF-L3-005).</t>
+  </si>
+  <si>
     <t>L4-Permissions  |  Ma trận uỷ quyền trên giao diện — 7 vai trò của SRS v2  |  NFR-SEC03; FT-09 NAC-01/NAC-02</t>
   </si>
   <si>
@@ -1157,6 +1178,12 @@
 Các thao tác quản trị kỹ thuật vẫn dùng bình thường</t>
   </si>
   <si>
+    <t>DEF-L4-005</t>
+  </si>
+  <si>
+    <t>API chan Admin dung (ceo-decision 403, inventory adjust 403) NHUNG UI van cho Admin mo /warehouse/inv-management/stock-adjustment va /ceo/* (App.tsx:76,79).</t>
+  </si>
+  <si>
     <t>/sales-manager/change-requests</t>
   </si>
   <si>
@@ -1215,6 +1242,12 @@
   <si>
     <t>Hệ thống tự refresh ngầm, thao tác thành công
 Người dùng KHÔNG bị đá ra trang đăng nhập</t>
+  </si>
+  <si>
+    <t>DEF-L4-006</t>
+  </si>
+  <si>
+    <t>KHONG on dinh — do 4/5 lan chay. Refresh token xoay vong moi lan refresh; authService.fetchWithToken khong co mutex nen request cham hon dung token da bi xoay -&gt; 401 -&gt; xoa phien va chuyen ve /login.</t>
   </si>
   <si>
     <t>Refresh token bị thu hồi (đăng xuất ở nơi khác)</t>
@@ -1264,6 +1297,12 @@
   <si>
     <t>Hiện cảnh báo giá đã hết hạn bằng tiếng Việt
 Bị chặn cho tới khi bấm làm mới và xác nhận lại giá</t>
+  </si>
+  <si>
+    <t>DEF-L4-007</t>
+  </si>
+  <si>
+    <t>Sau khi day Carts.UpdatedAt lui 24:00:01, gio van cho thanh toan; khong co canh bao gia het han va khong bat lam moi gia. Khong tim thay logic 24h o CartService lan Cart.jsx.</t>
   </si>
   <si>
     <t>L4-Responsive  |  NFR-U01 (&gt;= 375px) · NFR-U02 (tiếng Việt) · NFR-U03 (checkout &lt;= 4 bước)</t>
@@ -1435,6 +1474,12 @@
 Sau khi đăng: lưu link bài, hiện trong lịch sử</t>
   </si>
   <si>
+    <t>DEF-L4-004</t>
+  </si>
+  <si>
+    <t>Workbook ghi /admin/ai-marketing nhung route do la stub ComingSoon (AdminPortal.tsx:205-207). Chuc nang that o /sales/ai-content-studio.</t>
+  </si>
+  <si>
     <t>Bài M1 do chính Sales này tạo, đang chờ duyệt</t>
   </si>
   <si>
@@ -1477,6 +1522,9 @@
 Bài không gửi duyệt được khi đính kèm không hợp lệ</t>
   </si>
   <si>
+    <t>POST /api/marketing-posts/{id}/media -&gt; 404. Upload media chua trien khai; khong kiem duoc NFR-SEC07.</t>
+  </si>
+  <si>
     <t>Admin + Sales Manager</t>
   </si>
   <si>
@@ -1495,6 +1543,9 @@
     <t>Số liệu tương tác gắn đúng bài đã đăng
 Bài lỗi giữ nguyên nội dung đã duyệt, thử lại KHÔNG tạo bài trùng trên Facebook
 Khách A VẪN thuộc Sales S1</t>
+  </si>
+  <si>
+    <t>GET /api/marketing-posts/{id}/metrics -&gt; 404. Chi so tuong tac chua trien khai.</t>
   </si>
   <si>
     <t>Customer + Sales Manager + Sales Staff</t>
@@ -1515,6 +1566,9 @@
     <t>Khách theo dõi được tiến độ
 Sau khi thu hồi: hàng KHÔNG cộng vào tồn bán được
 Sales Staff không tự duyệt được yêu cầu</t>
+  </si>
+  <si>
+    <t>Workbook ghi /sales/pickup-arrangement nhung route khong ton tai trong SalesPortal.tsx (roi vao catch-all ve Dashboard).</t>
   </si>
   <si>
     <t>/sales/orders (tạo đơn thay thế)</t>
@@ -1757,7 +1811,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1795,51 +1849,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1950,13 +1978,54 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2238,356 +2307,356 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
     </row>
     <row r="4" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
     </row>
     <row r="5" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
     </row>
     <row r="7" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
     </row>
     <row r="8" spans="2:4" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
     </row>
     <row r="10" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
     </row>
     <row r="11" spans="2:4" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
     </row>
     <row r="13" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
     </row>
     <row r="14" spans="2:4" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
     </row>
     <row r="16" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
     </row>
     <row r="17" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
     </row>
     <row r="19" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
     </row>
     <row r="20" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="7"/>
+      <c r="D20" s="43"/>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="43"/>
     </row>
     <row r="22" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7"/>
+      <c r="D22" s="43"/>
     </row>
     <row r="23" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="43"/>
     </row>
     <row r="24" spans="2:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="7"/>
+      <c r="D24" s="43"/>
     </row>
     <row r="25" spans="2:4" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="43"/>
     </row>
     <row r="26" spans="2:4" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="7"/>
+      <c r="D26" s="43"/>
     </row>
     <row r="27" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="7"/>
+      <c r="D28" s="43"/>
     </row>
     <row r="29" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="6"/>
+      <c r="D29" s="43"/>
     </row>
     <row r="30" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="7"/>
+      <c r="D30" s="43"/>
     </row>
     <row r="32" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
     </row>
     <row r="34" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
     </row>
     <row r="35" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
     </row>
     <row r="36" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
     </row>
     <row r="37" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
     </row>
     <row r="38" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
     </row>
     <row r="39" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
     </row>
     <row r="40" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
     </row>
     <row r="42" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
     </row>
     <row r="43" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" s="43"/>
     </row>
     <row r="44" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" s="43"/>
     </row>
     <row r="45" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" s="43"/>
     </row>
     <row r="47" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="50" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="51" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="9" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2609,1415 +2678,1415 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="11">
         <f>COUNTA(A7:A798)</f>
         <v>47</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="11">
         <f>COUNTIF(E7:E798,"P1")</f>
         <v>35</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="11">
         <f>COUNTIF(E7:E798,"P2")</f>
         <v>12</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="11">
         <f>COUNTIF(E7:E798,"P3")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="11">
         <f>COUNTIF(F7:F798,"Yes")</f>
         <v>14</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="11">
         <f>COUNTIF(G7:G798,"Pass")</f>
+        <v>35</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="11">
+        <f>COUNTIF(G7:G798,"Fail")</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="11">
+        <f>COUNTIF(G7:G798,"Not Run")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="24">
-        <f>COUNTIF(G7:G798,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="24">
-        <f>COUNTIF(G7:G798,"Not Run")</f>
-        <v>47</v>
-      </c>
     </row>
     <row r="6" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="29" t="str">
+      <c r="G7" s="16" t="str">
         <f>'L4-CriticalPaths'!L6</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H7" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H7" s="16">
         <f>'L4-CriticalPaths'!M6</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="19" t="str">
         <f>'L4-CriticalPaths'!L7</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H8" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H8" s="19">
         <f>'L4-CriticalPaths'!M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="29" t="str">
+      <c r="G9" s="16" t="str">
         <f>'L4-CriticalPaths'!L8</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H9" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H9" s="16">
         <f>'L4-CriticalPaths'!M8</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="32" t="str">
+      <c r="G10" s="19" t="str">
         <f>'L4-CriticalPaths'!L9</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H10" s="32">
+        <v>Fail</v>
+      </c>
+      <c r="H10" s="19" t="str">
         <f>'L4-CriticalPaths'!M9</f>
-        <v>0</v>
+        <v>DEF-L4-001</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="29" t="str">
+      <c r="G11" s="16" t="str">
         <f>'L4-CriticalPaths'!L10</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H11" s="29">
+        <v>Blocked</v>
+      </c>
+      <c r="H11" s="16" t="str">
         <f>'L4-CriticalPaths'!M10</f>
-        <v>0</v>
+        <v>DEF-L4-002</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="32" t="str">
+      <c r="G12" s="19" t="str">
         <f>'L4-CriticalPaths'!L11</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H12" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H12" s="19">
         <f>'L4-CriticalPaths'!M11</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="29" t="str">
+      <c r="G13" s="16" t="str">
         <f>'L4-UserJourneys'!L6</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H13" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H13" s="16">
         <f>'L4-UserJourneys'!M6</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="32" t="str">
+      <c r="G14" s="19" t="str">
         <f>'L4-UserJourneys'!L7</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H14" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H14" s="19">
         <f>'L4-UserJourneys'!M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="29" t="str">
+      <c r="G15" s="16" t="str">
         <f>'L4-UserJourneys'!L8</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H15" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H15" s="16">
         <f>'L4-UserJourneys'!M8</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="32" t="str">
+      <c r="G16" s="19" t="str">
         <f>'L4-UserJourneys'!L9</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H16" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H16" s="19">
         <f>'L4-UserJourneys'!M9</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G17" s="29" t="str">
+      <c r="G17" s="16" t="str">
         <f>'L4-UserJourneys'!L11</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H17" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H17" s="16">
         <f>'L4-UserJourneys'!M11</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="32" t="str">
+      <c r="G18" s="19" t="str">
         <f>'L4-UserJourneys'!L12</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H18" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H18" s="19">
         <f>'L4-UserJourneys'!M12</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="29" t="str">
+      <c r="G19" s="16" t="str">
         <f>'L4-UserJourneys'!L14</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H19" s="29">
+        <v>Blocked</v>
+      </c>
+      <c r="H19" s="16" t="str">
         <f>'L4-UserJourneys'!M14</f>
-        <v>0</v>
+        <v>DEF-L4-002</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G20" s="32" t="str">
+      <c r="G20" s="19" t="str">
         <f>'L4-UserJourneys'!L15</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H20" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H20" s="19">
         <f>'L4-UserJourneys'!M15</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G21" s="29" t="str">
+      <c r="G21" s="16" t="str">
         <f>'L4-UserJourneys'!L16</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H21" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H21" s="16">
         <f>'L4-UserJourneys'!M16</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="32" t="str">
+      <c r="G22" s="19" t="str">
         <f>'L4-UserJourneys'!L18</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H22" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H22" s="19">
         <f>'L4-UserJourneys'!M18</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G23" s="29" t="str">
+      <c r="G23" s="16" t="str">
         <f>'L4-UserJourneys'!L19</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H23" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H23" s="16">
         <f>'L4-UserJourneys'!M19</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="32" t="str">
+      <c r="G24" s="19" t="str">
         <f>'L4-UserJourneys'!L20</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H24" s="32">
+        <v>Blocked</v>
+      </c>
+      <c r="H24" s="19" t="str">
         <f>'L4-UserJourneys'!M20</f>
-        <v>0</v>
+        <v>DEF-L4-003</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G25" s="29" t="str">
+      <c r="G25" s="16" t="str">
         <f>'L4-UserJourneys'!L21</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H25" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H25" s="16">
         <f>'L4-UserJourneys'!M21</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G26" s="32" t="str">
+      <c r="G26" s="19" t="str">
         <f>'L4-UserJourneys'!L22</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H26" s="32">
+        <v>Blocked</v>
+      </c>
+      <c r="H26" s="19" t="str">
         <f>'L4-UserJourneys'!M22</f>
-        <v>0</v>
+        <v>DEF-L4-003</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="29" t="str">
+      <c r="G27" s="16" t="str">
         <f>'L4-Permissions'!L6</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H27" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H27" s="16">
         <f>'L4-Permissions'!M6</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="32" t="str">
+      <c r="G28" s="19" t="str">
         <f>'L4-Permissions'!L7</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H28" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H28" s="19">
         <f>'L4-Permissions'!M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="29" t="str">
+      <c r="G29" s="16" t="str">
         <f>'L4-Permissions'!L8</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H29" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H29" s="16">
         <f>'L4-Permissions'!M8</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E30" s="28" t="s">
+      <c r="E30" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="32" t="str">
+      <c r="G30" s="19" t="str">
         <f>'L4-Permissions'!L9</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H30" s="32">
+        <v>Fail</v>
+      </c>
+      <c r="H30" s="19" t="str">
         <f>'L4-Permissions'!M9</f>
-        <v>0</v>
+        <v>DEF-L4-005</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="29" t="str">
+      <c r="G31" s="16" t="str">
         <f>'L4-Permissions'!L10</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H31" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H31" s="16">
         <f>'L4-Permissions'!M10</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="31" t="s">
+      <c r="F32" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="32" t="str">
+      <c r="G32" s="19" t="str">
         <f>'L4-Permissions'!L11</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H32" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H32" s="19">
         <f>'L4-Permissions'!M11</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="29" t="str">
+      <c r="G33" s="16" t="str">
         <f>'L4-Permissions'!L12</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H33" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H33" s="16">
         <f>'L4-Permissions'!M12</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G34" s="32" t="str">
+      <c r="G34" s="19" t="str">
         <f>'L4-SessionManagement'!L6</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H34" s="32">
+        <v>Fail</v>
+      </c>
+      <c r="H34" s="19" t="str">
         <f>'L4-SessionManagement'!M6</f>
-        <v>0</v>
+        <v>DEF-L4-006</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="29" t="str">
+      <c r="G35" s="16" t="str">
         <f>'L4-SessionManagement'!L7</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H35" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H35" s="16">
         <f>'L4-SessionManagement'!M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="28" t="s">
+      <c r="E36" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="32" t="str">
+      <c r="G36" s="19" t="str">
         <f>'L4-SessionManagement'!L8</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H36" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H36" s="19">
         <f>'L4-SessionManagement'!M8</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E37" s="28" t="s">
+      <c r="E37" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G37" s="29" t="str">
+      <c r="G37" s="16" t="str">
         <f>'L4-SessionManagement'!L9</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H37" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H37" s="16">
         <f>'L4-SessionManagement'!M9</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="32" t="str">
+      <c r="G38" s="19" t="str">
         <f>'L4-SessionManagement'!L10</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H38" s="32">
+        <v>Fail</v>
+      </c>
+      <c r="H38" s="19" t="str">
         <f>'L4-SessionManagement'!M10</f>
-        <v>0</v>
+        <v>DEF-L4-007</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="E39" s="28" t="s">
+      <c r="E39" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G39" s="29" t="str">
+      <c r="G39" s="16" t="str">
         <f>'L4-Responsive (Optional)'!L6</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H39" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H39" s="16">
         <f>'L4-Responsive (Optional)'!M6</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E40" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="32" t="str">
+      <c r="G40" s="19" t="str">
         <f>'L4-Responsive (Optional)'!L7</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H40" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H40" s="19">
         <f>'L4-Responsive (Optional)'!M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="E41" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="F41" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G41" s="29" t="str">
+      <c r="G41" s="16" t="str">
         <f>'L4-Responsive (Optional)'!L8</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H41" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H41" s="16">
         <f>'L4-Responsive (Optional)'!M8</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="31" t="s">
+      <c r="F42" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G42" s="32" t="str">
+      <c r="G42" s="19" t="str">
         <f>'L4-Responsive (Optional)'!L9</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H42" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H42" s="19">
         <f>'L4-Responsive (Optional)'!M9</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="E43" s="28" t="s">
+      <c r="E43" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="27" t="s">
+      <c r="F43" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G43" s="29" t="str">
+      <c r="G43" s="16" t="str">
         <f>'L4-AdminMarketing'!L6</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H43" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H43" s="16">
         <f>'L4-AdminMarketing'!M6</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="E44" s="28" t="s">
+      <c r="E44" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F44" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G44" s="32" t="str">
+      <c r="G44" s="19" t="str">
         <f>'L4-AdminMarketing'!L7</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H44" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H44" s="19">
         <f>'L4-AdminMarketing'!M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E45" s="28" t="s">
+      <c r="E45" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G45" s="29" t="str">
+      <c r="G45" s="16" t="str">
         <f>'L4-AdminMarketing'!L8</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H45" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H45" s="16">
         <f>'L4-AdminMarketing'!M8</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C46" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E46" s="28" t="s">
+      <c r="E46" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G46" s="32" t="str">
+      <c r="G46" s="19" t="str">
         <f>'L4-AdminMarketing'!L9</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H46" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H46" s="19">
         <f>'L4-AdminMarketing'!M9</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E47" s="28" t="s">
+      <c r="E47" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F47" s="27" t="s">
+      <c r="F47" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G47" s="29" t="str">
+      <c r="G47" s="16" t="str">
         <f>'L4-AdminMarketing'!L11</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H47" s="29">
+        <v>Blocked</v>
+      </c>
+      <c r="H47" s="16" t="str">
         <f>'L4-AdminMarketing'!M11</f>
-        <v>0</v>
+        <v>DEF-L4-004</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C48" s="31" t="s">
+      <c r="C48" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D48" s="31" t="s">
+      <c r="D48" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E48" s="28" t="s">
+      <c r="E48" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F48" s="31" t="s">
+      <c r="F48" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G48" s="32" t="str">
+      <c r="G48" s="19" t="str">
         <f>'L4-AdminMarketing'!L12</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H48" s="32">
+        <v>Pass</v>
+      </c>
+      <c r="H48" s="19">
         <f>'L4-AdminMarketing'!M12</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="27" t="s">
+      <c r="D49" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E49" s="28" t="s">
+      <c r="E49" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F49" s="27" t="s">
+      <c r="F49" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G49" s="29" t="str">
+      <c r="G49" s="16" t="str">
         <f>'L4-AdminMarketing'!L13</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H49" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H49" s="16">
         <f>'L4-AdminMarketing'!M13</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="31" t="s">
+      <c r="D50" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E50" s="28" t="s">
+      <c r="E50" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G50" s="32" t="str">
+      <c r="G50" s="19" t="str">
         <f>'L4-AdminMarketing'!L14</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H50" s="32">
+        <v>Blocked</v>
+      </c>
+      <c r="H50" s="19" t="str">
         <f>'L4-AdminMarketing'!M14</f>
-        <v>0</v>
+        <v>DEF-L4-003</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E51" s="28" t="s">
+      <c r="E51" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="27" t="s">
+      <c r="F51" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G51" s="29" t="str">
+      <c r="G51" s="16" t="str">
         <f>'L4-AdminMarketing'!L15</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H51" s="29">
+        <v>Blocked</v>
+      </c>
+      <c r="H51" s="16" t="str">
         <f>'L4-AdminMarketing'!M15</f>
-        <v>0</v>
+        <v>DEF-L4-003</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="31" t="s">
+      <c r="C52" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="28" t="s">
+      <c r="E52" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F52" s="31" t="s">
+      <c r="F52" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G52" s="32" t="str">
+      <c r="G52" s="19" t="str">
         <f>'L4-AdminMarketing'!L16</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H52" s="32">
+        <v>Blocked</v>
+      </c>
+      <c r="H52" s="19" t="str">
         <f>'L4-AdminMarketing'!M16</f>
-        <v>0</v>
+        <v>DEF-L4-004</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="E53" s="28" t="s">
+      <c r="E53" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="27" t="s">
+      <c r="F53" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G53" s="29" t="str">
+      <c r="G53" s="16" t="str">
         <f>'L4-AdminMarketing'!L17</f>
-        <v>Not Run</v>
-      </c>
-      <c r="H53" s="29">
+        <v>Pass</v>
+      </c>
+      <c r="H53" s="16">
         <f>'L4-AdminMarketing'!M17</f>
         <v>0</v>
       </c>
@@ -4052,82 +4121,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="20" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4135,323 +4204,331 @@
       <c r="A5" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="K6" s="36" t="s">
+      <c r="K6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+    </row>
+    <row r="8" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="N9" s="27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+    </row>
+    <row r="13" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-    </row>
-    <row r="7" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-    </row>
-    <row r="8" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-    </row>
-    <row r="10" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="K10" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-    </row>
-    <row r="11" spans="1:14" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="J11" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="K11" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-    </row>
-    <row r="13" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="J13" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="K13" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A12:N12"/>
   </mergeCells>
   <dataValidations count="2">
@@ -4490,783 +4567,795 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="A1" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="20" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
+        <v>230</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="37" t="s">
+      <c r="D6" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="I6" s="36" t="s">
+      <c r="F6" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="J6" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="K6" s="36" t="s">
+      <c r="C7" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="K7" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-    </row>
-    <row r="7" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="E7" s="37" t="s">
+      <c r="L7" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+    </row>
+    <row r="8" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F8" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>235</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="K7" s="40" t="s">
+      <c r="G9" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="K9" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="L7" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-    </row>
-    <row r="8" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
+      <c r="L9" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="54" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
+        <v>251</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
     </row>
     <row r="11" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" s="36" t="s">
+      <c r="B11" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="D11" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="J11" s="36" t="s">
+      <c r="F11" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="G11" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="K11" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
+      <c r="L11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
     </row>
     <row r="12" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C12" s="40" t="s">
+      <c r="B12" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="40" t="s">
-        <v>254</v>
-      </c>
-      <c r="G12" s="40" t="s">
-        <v>255</v>
-      </c>
-      <c r="H12" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="I12" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="J12" s="40" t="s">
+      <c r="F12" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="G12" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="K12" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="L12" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
+      <c r="L12" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="54" t="s">
-        <v>259</v>
-      </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
+        <v>263</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
     </row>
     <row r="14" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="36" t="s">
+      <c r="B14" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="E14" s="37" t="s">
+      <c r="D14" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="H14" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="K14" s="36" t="s">
+      <c r="F14" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="K14" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
+      <c r="L14" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="40" t="s">
+      <c r="B15" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="E15" s="37" t="s">
+      <c r="D15" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>265</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="I15" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="J15" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="K15" s="40" t="s">
+      <c r="F15" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="J15" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="K15" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="L15" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
+      <c r="L15" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="36" t="s">
+      <c r="B16" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="G16" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="H16" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="J16" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="K16" s="36" t="s">
+      <c r="G16" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="K16" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L16" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
+      <c r="L16" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
     </row>
     <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="s">
-        <v>273</v>
-      </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
+        <v>278</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
     </row>
     <row r="18" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+    </row>
+    <row r="19" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="I19" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="J19" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+    </row>
+    <row r="20" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="I21" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="J21" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+    </row>
+    <row r="22" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+    </row>
+    <row r="24" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="I24" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="H18" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>279</v>
-      </c>
-      <c r="K18" s="36" t="s">
+      <c r="J24" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K24" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L24" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-    </row>
-    <row r="19" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="K19" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L19" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-    </row>
-    <row r="20" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="L20" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-    </row>
-    <row r="21" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="J21" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="K21" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-    </row>
-    <row r="22" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="J22" s="36" t="s">
-        <v>298</v>
-      </c>
-      <c r="K22" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="L22" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-    </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-    </row>
-    <row r="24" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="L24" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A23:N23"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A10:N10"/>
     <mergeCell ref="A13:N13"/>
   </mergeCells>
   <dataValidations count="2">
@@ -5305,447 +5394,451 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="A1" s="55" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="20" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>300</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
+        <v>308</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="37" t="s">
+      <c r="D6" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="K6" s="41" t="s">
+      <c r="F6" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="K6" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="30"/>
+    </row>
+    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L9" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+    </row>
+    <row r="11" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="30"/>
+    </row>
+    <row r="12" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+    </row>
+    <row r="14" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-    </row>
-    <row r="7" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="K7" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="40"/>
-      <c r="N7" s="43"/>
-    </row>
-    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>311</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>312</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>314</v>
-      </c>
-      <c r="K8" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>315</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>318</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="K9" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="43"/>
-    </row>
-    <row r="10" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>320</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>322</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="L10" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-    </row>
-    <row r="11" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>324</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>325</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>326</v>
-      </c>
-      <c r="J11" s="40" t="s">
-        <v>327</v>
-      </c>
-      <c r="K11" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="40"/>
-      <c r="N11" s="43"/>
-    </row>
-    <row r="12" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="J12" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="L12" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-    </row>
-    <row r="14" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="J14" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
     <mergeCell ref="A5:N5"/>
     <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="L6:L12 L14" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -5783,367 +5876,375 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="A1" s="55" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="20" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>333</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
+        <v>343</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="37" t="s">
+      <c r="D6" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>337</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>338</v>
-      </c>
-      <c r="K6" s="36" t="s">
+      <c r="G6" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+    </row>
+    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+    </row>
+    <row r="10" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+    </row>
+    <row r="12" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-    </row>
-    <row r="7" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>341</v>
-      </c>
-      <c r="K7" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-    </row>
-    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>342</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>343</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>344</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>345</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>346</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>347</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>348</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>349</v>
-      </c>
-      <c r="K9" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-    </row>
-    <row r="10" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>346</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>350</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>352</v>
-      </c>
-      <c r="K10" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="L10" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="55"/>
-    </row>
-    <row r="12" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="J12" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="L12" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A11:N11"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A11:N11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="L6:L10 L12" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -6181,326 +6282,326 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="A1" s="55" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="20" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
+        <v>368</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>355</v>
-      </c>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="44" t="s">
+      <c r="D6" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>356</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>357</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>358</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>359</v>
-      </c>
-      <c r="K6" s="36" t="s">
+      <c r="G6" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>374</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="30"/>
+    </row>
+    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="30"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+    </row>
+    <row r="11" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-    </row>
-    <row r="7" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>355</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>360</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>362</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>363</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="40"/>
-      <c r="N7" s="43"/>
-    </row>
-    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>365</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>366</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>367</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>369</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>370</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>373</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="43"/>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-    </row>
-    <row r="11" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="K11" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A10:N10"/>
   </mergeCells>
   <dataValidations count="2">
@@ -6539,566 +6640,582 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>374</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
+      <c r="A1" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
-        <v>375</v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="A2" s="56" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="25" t="s">
+      <c r="M4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="25" t="s">
+      <c r="N4" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>376</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
+        <v>390</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" s="28" t="s">
+      <c r="D6" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="48" t="s">
-        <v>315</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>377</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>378</v>
-      </c>
-      <c r="I6" s="48" t="s">
-        <v>379</v>
-      </c>
-      <c r="J6" s="48" t="s">
-        <v>380</v>
-      </c>
-      <c r="K6" s="48" t="s">
+      <c r="F6" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="I6" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="K6" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="48"/>
-      <c r="N6" s="50"/>
+      <c r="L6" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="35"/>
+      <c r="N6" s="37"/>
     </row>
     <row r="7" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="31" t="s">
+      <c r="B7" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="28" t="s">
+      <c r="D7" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>382</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>384</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="K7" s="31" t="s">
+      <c r="F7" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="K7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="L7" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="31"/>
-      <c r="N7" s="51"/>
+      <c r="L7" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="18"/>
+      <c r="N7" s="38"/>
     </row>
     <row r="8" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="C8" s="48" t="s">
+      <c r="B8" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>306</v>
-      </c>
-      <c r="E8" s="28" t="s">
+      <c r="D8" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="48" t="s">
-        <v>315</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>386</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>387</v>
-      </c>
-      <c r="I8" s="48" t="s">
-        <v>388</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>389</v>
-      </c>
-      <c r="K8" s="48" t="s">
+      <c r="F8" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>402</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="K8" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="L8" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="48"/>
-      <c r="N8" s="50"/>
+      <c r="L8" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="35"/>
+      <c r="N8" s="37"/>
     </row>
     <row r="9" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="E9" s="28" t="s">
+      <c r="D9" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>390</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>391</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>393</v>
-      </c>
-      <c r="K9" s="31" t="s">
+      <c r="F9" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="K9" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="L9" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="31"/>
-      <c r="N9" s="51"/>
+      <c r="L9" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="18"/>
+      <c r="N9" s="38"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="54" t="s">
-        <v>394</v>
-      </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
+        <v>408</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
     </row>
     <row r="11" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B11" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" s="48" t="s">
+      <c r="B11" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>395</v>
-      </c>
-      <c r="E11" s="28" t="s">
+      <c r="D11" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="48" t="s">
-        <v>396</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>397</v>
-      </c>
-      <c r="H11" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="I11" s="48" t="s">
-        <v>399</v>
-      </c>
-      <c r="J11" s="48" t="s">
-        <v>400</v>
-      </c>
-      <c r="K11" s="48" t="s">
+      <c r="F11" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="K11" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="48"/>
-      <c r="N11" s="50"/>
+      <c r="L11" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>415</v>
+      </c>
+      <c r="N11" s="37" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="C12" s="31" t="s">
+      <c r="B12" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="E12" s="28" t="s">
+      <c r="D12" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>397</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>401</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>402</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="K12" s="31" t="s">
+      <c r="F12" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="K12" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="L12" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="31"/>
-      <c r="N12" s="51"/>
+      <c r="L12" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="38"/>
     </row>
     <row r="13" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C13" s="48" t="s">
+      <c r="B13" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="48" t="s">
-        <v>395</v>
-      </c>
-      <c r="E13" s="28" t="s">
+      <c r="D13" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="48" t="s">
-        <v>254</v>
-      </c>
-      <c r="G13" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="H13" s="48" t="s">
-        <v>405</v>
-      </c>
-      <c r="I13" s="48" t="s">
-        <v>406</v>
-      </c>
-      <c r="J13" s="48" t="s">
-        <v>407</v>
-      </c>
-      <c r="K13" s="48" t="s">
+      <c r="F13" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="J13" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="K13" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="L13" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="48"/>
-      <c r="N13" s="50"/>
+      <c r="L13" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="35"/>
+      <c r="N13" s="37"/>
     </row>
     <row r="14" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B14" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="E14" s="28" t="s">
+      <c r="D14" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>404</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>408</v>
-      </c>
-      <c r="I14" s="31" t="s">
+      <c r="F14" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="N14" s="38" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="35" t="s">
         <v>409</v>
       </c>
-      <c r="J14" s="31" t="s">
-        <v>410</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="L14" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="31"/>
-      <c r="N14" s="51"/>
-    </row>
-    <row r="15" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="48" t="s">
-        <v>395</v>
-      </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="48" t="s">
-        <v>411</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>412</v>
-      </c>
-      <c r="H15" s="48" t="s">
-        <v>413</v>
-      </c>
-      <c r="I15" s="48" t="s">
-        <v>414</v>
-      </c>
-      <c r="J15" s="48" t="s">
+      <c r="F15" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>429</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="K15" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="N15" s="37" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="K15" s="48" t="s">
+      <c r="N16" s="38" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>441</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>443</v>
+      </c>
+      <c r="K17" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="L15" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="50"/>
-    </row>
-    <row r="16" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>416</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="I16" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="K16" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="L16" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" s="31"/>
-      <c r="N16" s="51"/>
-    </row>
-    <row r="17" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>264</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="48" t="s">
-        <v>421</v>
-      </c>
-      <c r="H17" s="48" t="s">
-        <v>422</v>
-      </c>
-      <c r="I17" s="48" t="s">
-        <v>423</v>
-      </c>
-      <c r="J17" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="K17" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="L17" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17" s="48"/>
-      <c r="N17" s="50"/>
+      <c r="L17" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="35"/>
+      <c r="N17" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A10:N10"/>
   </mergeCells>
   <dataValidations count="2">
